--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2528,6 +2528,67 @@
         <v>7717.13</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3084-121-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.967.700-5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>77339.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3082-651-CM25</t>
+          <t>4686-101-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7928.26</v>
+        <v>32540.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2832-3466-CM25</t>
+          <t>3108-34-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>61.926.100-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7189.74</v>
+        <v>1812.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3191-6161-CM25</t>
+          <t>3082-651-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2063.75</v>
+        <v>7928.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2698-338-CM25</t>
+          <t>2832-3466-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>73669.92999999999</v>
+        <v>7189.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>318-199-CM25</t>
+          <t>3191-6161-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.816.800-9</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9939.360000000001</v>
+        <v>2063.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1431841-3-CM26</t>
+          <t>2698-338-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1713.22</v>
+        <v>73669.92999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4301-86-CM26</t>
+          <t>318-199-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.816.800-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30158.88</v>
+        <v>9939.360000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>1431841-3-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>859.89</v>
+        <v>1713.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>4301-86-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>30771.02</v>
+        <v>30158.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2696-18-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6416.48</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3778-54-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12418.36</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1035206-31-CM26</t>
+          <t>2696-18-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8463.99</v>
+        <v>6416.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4766-3405-CM26</t>
+          <t>3778-54-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13305.39</v>
+        <v>12418.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>619568-36-CM26</t>
+          <t>1035206-31-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>35481.04</v>
+        <v>8463.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3776-128-CM26</t>
+          <t>4766-3405-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21288.62</v>
+        <v>13305.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-295-CM26</t>
+          <t>619568-36-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3457.31</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2211-345-CM26</t>
+          <t>3776-128-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5859.56</v>
+        <v>21288.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2026-295-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17387.27</v>
+        <v>3457.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>2211-345-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13205.43</v>
+        <v>5859.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2427-296-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>55977.6</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1048-124-CM26</t>
+          <t>2427-295-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>41279.32</v>
+        <v>13205.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3157-25-CM26</t>
+          <t>2427-296-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1951.46</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2594-437-CM26</t>
+          <t>1048-124-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2113.44</v>
+        <v>41279.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>568658-841-CM26</t>
+          <t>3157-25-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3170.16</v>
+        <v>1951.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3232-355-CM26</t>
+          <t>2594-437-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37609.95</v>
+        <v>2113.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3678-177-CM26</t>
+          <t>568658-841-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14608.44</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3882-209-CM26</t>
+          <t>3232-355-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17740.52</v>
+        <v>37609.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>3678-177-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,32 +2201,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>150600.45</v>
+        <v>14608.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>3882-209-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6761.87</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,28 +2323,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>887.03</v>
+        <v>150600.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3693-113-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11602.5</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5226.19</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>3693-113-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7717.13</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,6 +2586,128 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
+        <v>5226.19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3692-270-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.061.700-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>7717.13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3084-121-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.967.700-5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>77339.91</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4686-101-CM25</t>
+          <t>4280-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32540.55</v>
+        <v>31930.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3108-34-CM25</t>
+          <t>568658-134-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.926.100-3</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1812.93</v>
+        <v>31420.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3082-651-CM25</t>
+          <t>4686-101-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7928.26</v>
+        <v>32540.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2832-3466-CM25</t>
+          <t>2696-9-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7189.74</v>
+        <v>6157.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3191-6161-CM25</t>
+          <t>4301-172-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2063.75</v>
+        <v>30183.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2698-338-CM25</t>
+          <t>1035206-28-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>73669.92999999999</v>
+        <v>7694.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>318-199-CM25</t>
+          <t>3134-35-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.816.800-9</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9939.360000000001</v>
+        <v>15091.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1431841-3-CM26</t>
+          <t>4290-35-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1713.22</v>
+        <v>8508.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4301-86-CM26</t>
+          <t>2427-269-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>30158.88</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>4766-110-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>859.89</v>
+        <v>13316.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>1048-146-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>30771.02</v>
+        <v>35421.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2696-18-CM26</t>
+          <t>3776-186-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6416.48</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3778-54-CM26</t>
+          <t>3073-229-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12418.36</v>
+        <v>8809.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1035206-31-CM26</t>
+          <t>3621-135-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8463.99</v>
+        <v>16512.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4766-3405-CM26</t>
+          <t>3108-34-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>61.926.100-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13305.39</v>
+        <v>1812.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>619568-36-CM26</t>
+          <t>2424-942-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,20 +1477,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>35481.04</v>
+        <v>980179.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3776-128-CM26</t>
+          <t>3882-175-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1504,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21288.62</v>
+        <v>13316.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-295-CM26</t>
+          <t>3157-36-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1565,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3457.31</v>
+        <v>798.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2211-345-CM26</t>
+          <t>2026-1019-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1626,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5859.56</v>
+        <v>6424.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>3232-391-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17387.27</v>
+        <v>47158.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>2026-1439-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1778,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13205.43</v>
+        <v>242260.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2427-296-CM26</t>
+          <t>4555-190-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1813,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1828,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1843,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>55977.6</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1048-124-CM26</t>
+          <t>2598-180-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1874,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1904,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1919,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41279.32</v>
+        <v>4711.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3157-25-CM26</t>
+          <t>4044-655-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1935,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1950,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1980,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1951.46</v>
+        <v>53116.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2594-437-CM26</t>
+          <t>4290-116-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1996,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2011,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2026,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2041,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2113.44</v>
+        <v>7735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>568658-841-CM26</t>
+          <t>859378-575-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2057,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2072,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2087,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2102,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3170.16</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3232-355-CM26</t>
+          <t>1725-5533-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2118,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2148,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2163,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>37609.95</v>
+        <v>346215.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3678-177-CM26</t>
+          <t>2594-926-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2179,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2194,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2209,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2224,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14608.44</v>
+        <v>5286.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3882-209-CM26</t>
+          <t>3275-277-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2240,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2255,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2270,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2285,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17740.52</v>
+        <v>7401.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>836-190-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2301,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,32 +2331,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>150600.45</v>
+        <v>41563.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>3275-282-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2362,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2377,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2407,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6761.87</v>
+        <v>37219.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>3275-281-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2423,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2453,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>887.03</v>
+        <v>4229.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3693-113-CM26</t>
+          <t>3275-278-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,27 +2484,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2514,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2529,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11602.5</v>
+        <v>4440.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>2428-1603-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2545,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2575,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5226.19</v>
+        <v>62141.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>3082-651-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2606,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2621,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2636,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7717.13</v>
+        <v>7928.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>2832-3466-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2667,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2682,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2697,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,7 +2712,2146 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
+        <v>7189.74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3191-6161-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>2063.75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2698-338-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>73669.92999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>318-199-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>70.816.800-9</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>9939.360000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1431841-3-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.254.800-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1713.22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4301-86-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>30158.88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1704-946-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>859.89</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>568658-365-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>70.872.300-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>30771.02</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2696-18-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>6416.48</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3778-54-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>12418.36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1035206-31-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>65.165.411-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>8463.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4766-3405-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.060.200-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>13305.39</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>619568-36-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.050.600-9</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>35481.04</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3776-128-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>21288.62</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-295-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3457.31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2211-345-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>5859.56</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3621-125-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.050.200-3</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>17387.27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2427-295-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>13205.43</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2427-296-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>MSLI Latam Inc.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>55977.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1048-124-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>41279.32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3157-25-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.102.016-3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1951.46</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2594-437-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>73.568.600-3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCON</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>2113.44</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>568658-841-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>70.872.300-2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3170.16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3232-355-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>37609.95</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3678-177-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.050.500-2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>14608.44</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3882-209-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.060.400-0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>17740.52</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3515-294-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.060.300-4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>150600.45</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4077-104-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.979.360-9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>6761.87</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2424-859-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>887.03</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3693-113-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.061.700-5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>11602.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3073-290-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.102.015-5</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>5226.19</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3692-270-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.061.700-5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>7717.13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3084-121-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.967.700-5</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>77339.91</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3134-170-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>15079.44</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>836-127-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>72.235.100-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL V REGION</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>46156.53</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1202333-127-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.060.700-K</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>27892.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2427-269-CM25</t>
+          <t>4766-110-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>55977.6</v>
+        <v>13316.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4766-110-CM25</t>
+          <t>2427-269-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13316.1</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1048-146-CM25</t>
+          <t>3776-186-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35421.54</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3776-186-CM25</t>
+          <t>1048-146-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10652.88</v>
+        <v>35421.54</v>
       </c>
     </row>
     <row r="14">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1431841-3-CM26</t>
+          <t>4301-86-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2911,27 +2911,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1713.22</v>
+        <v>30158.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4301-86-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>30158.88</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>859.89</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>2696-18-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>30771.02</v>
+        <v>6416.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2696-18-CM26</t>
+          <t>3778-54-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3160,22 +3160,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6416.48</v>
+        <v>12418.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3778-54-CM26</t>
+          <t>1035206-31-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3216,27 +3216,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12418.36</v>
+        <v>8463.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1035206-31-CM26</t>
+          <t>4766-3405-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8463.99</v>
+        <v>13305.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4766-3405-CM26</t>
+          <t>619568-36-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,22 +3343,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13305.39</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>619568-36-CM26</t>
+          <t>3776-128-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3404,22 +3404,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>35481.04</v>
+        <v>21288.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3776-128-CM26</t>
+          <t>2026-295-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>21288.62</v>
+        <v>3457.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-295-CM26</t>
+          <t>2211-345-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3526,22 +3526,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3457.31</v>
+        <v>5859.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2211-345-CM26</t>
+          <t>2427-296-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5859.56</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="53">
@@ -3755,7 +3755,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2427-296-CM26</t>
+          <t>1048-124-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3810,13 +3810,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>55977.6</v>
+        <v>41279.32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1048-124-CM26</t>
+          <t>3157-25-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3871,13 +3871,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41279.32</v>
+        <v>1951.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3157-25-CM26</t>
+          <t>2594-437-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3892,22 +3892,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1951.46</v>
+        <v>2113.44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2594-437-CM26</t>
+          <t>568658-841-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3953,22 +3953,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2113.44</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>568658-841-CM26</t>
+          <t>3232-355-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3170.16</v>
+        <v>37609.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3232-355-CM26</t>
+          <t>3678-177-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4075,22 +4075,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>37609.95</v>
+        <v>14608.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3678-177-CM26</t>
+          <t>3882-209-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4136,22 +4136,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>14608.44</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3882-209-CM26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4197,22 +4197,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4222,28 +4222,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17740.52</v>
+        <v>150600.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4253,12 +4257,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4268,12 +4272,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4283,26 +4287,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>150600.45</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="64">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>3693-113-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>887.03</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3693-113-CM26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11602.5</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>3692-270-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5226.19</v>
+        <v>7717.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>3084-121-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4562,27 +4562,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7717.13</v>
+        <v>77339.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>3134-170-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>77339.91</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3134-170-CM26</t>
+          <t>836-127-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4689,22 +4689,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>15079.44</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>1202333-127-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4790,13 +4790,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>46156.53</v>
+        <v>27892.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>2799-897-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4806,12 +4806,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4836,22 +4836,331 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>218446.87</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1049-1453-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.310.000-8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>2579.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1080157-134-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.979.360-9</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>27892.7</v>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>2747.01</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4728-326-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>60.719.000-3</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>7221.61</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>907581-33-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>57477</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4044-689-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.061.800-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>58970.45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1124,7 +1160,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3776-186-CM25</t>
+          <t>1048-146-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,20 +1208,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10652.88</v>
+        <v>35421.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1048-146-CM25</t>
+          <t>3776-186-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1250,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1233,14 +1273,18 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>35421.54</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="14">
@@ -1294,7 +1338,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1598,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1663,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1728,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1793,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1923,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1988,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2053,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2179,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2305,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2278,7 +2370,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2435,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2500,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2565,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2522,7 +2630,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2583,7 +2695,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2644,7 +2760,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2705,7 +2825,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2766,7 +2890,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2827,7 +2955,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2888,7 +3020,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2949,7 +3085,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3010,7 +3150,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3071,7 +3215,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3132,7 +3280,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3345,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3410,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3475,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3540,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3605,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3670,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3735,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3633,7 +3813,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2427-295-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3653,17 +3833,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,28 +3853,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17387.27</v>
+        <v>13205.43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3714,17 +3898,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3734,22 +3918,26 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>13205.43</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="55">
@@ -3803,7 +3991,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3864,7 +4056,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,7 +4121,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4186,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4047,7 +4251,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4108,7 +4316,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4169,7 +4381,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4182,7 +4398,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>3084-86-SE26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4202,17 +4418,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4222,12 +4438,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4241,13 +4457,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>150600.45</v>
+        <v>51562.03</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4257,12 +4473,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4272,12 +4488,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4287,28 +4503,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>887.03</v>
+        <v>150600.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4328,17 +4548,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4348,28 +4568,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6761.87</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3693-113-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4384,22 +4608,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4409,28 +4633,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11602.5</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>3693-113-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4445,7 +4673,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4455,12 +4683,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4470,12 +4698,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4485,13 +4713,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5226.19</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4506,7 +4734,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4516,12 +4744,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4531,28 +4759,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7717.13</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3084-121-CM26</t>
+          <t>3692-270-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4562,27 +4794,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4592,28 +4824,32 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>77339.91</v>
+        <v>7717.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3134-170-CM26</t>
+          <t>3084-121-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4628,7 +4864,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4638,7 +4874,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4653,28 +4889,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>15079.44</v>
+        <v>77339.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>3134-170-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4689,22 +4929,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4722,20 +4962,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>46156.53</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>836-127-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4750,7 +4994,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4760,12 +5004,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4775,28 +5019,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>27892.7</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2799-897-CM26</t>
+          <t>1202333-127-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4806,12 +5054,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4821,12 +5069,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4836,17 +5084,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4855,13 +5103,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>218446.87</v>
+        <v>27892.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1049-1453-CM26</t>
+          <t>2799-897-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4876,7 +5124,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4886,12 +5134,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4901,28 +5149,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2579.15</v>
+        <v>218446.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1080157-134-CM26</t>
+          <t>1049-1453-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4942,17 +5194,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4962,28 +5214,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2747.01</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4728-326-CM26</t>
+          <t>1080157-134-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4998,7 +5254,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5008,12 +5264,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.719.000-3</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5023,28 +5279,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7221.61</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>907581-33-CM26</t>
+          <t>4728-326-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5059,22 +5319,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>60.719.000-3</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5084,82 +5344,155 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>57477</v>
+        <v>7221.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>907581-33-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>57477</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>4044-689-CM26</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>69.061.800-1</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="n">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
         <v>58970.45</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1160,7 +1160,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1048-146-CM25</t>
+          <t>3776-186-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35421.54</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3776-186-CM25</t>
+          <t>1048-146-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10652.88</v>
+        <v>35421.54</v>
       </c>
     </row>
     <row r="14">
@@ -3752,7 +3752,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2427-296-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3792,22 +3792,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>55977.6</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="53">
@@ -3878,7 +3882,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2427-296-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3898,17 +3902,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3918,26 +3922,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>880443249</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17387.27</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="55">
@@ -4398,7 +4398,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3084-86-SE26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4418,17 +4418,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>51562.03</v>
+        <v>150600.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3515-294-CM26</t>
+          <t>3084-86-SE26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4483,17 +4483,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>150600.45</v>
+        <v>51562.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4568,17 +4568,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4587,13 +4587,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>887.03</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4613,17 +4613,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4633,17 +4633,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6761.87</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="66">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5174,7 +5174,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1049-1453-CM26</t>
+          <t>1080157-134-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5194,17 +5194,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2579.15</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1080157-134-CM26</t>
+          <t>1049-1453-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5279,17 +5279,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2747.01</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="76">
@@ -5494,6 +5494,136 @@
       </c>
       <c r="M78" s="2" t="n">
         <v>58970.45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3776-516-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1171.82</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>701-631-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>20230.48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/valparaiso.xlsx
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
